--- a/fhir/ig/laboratorio/v0.1.0/StructureDefinition-MinsalEspecimenLaboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/StructureDefinition-MinsalEspecimenLaboratorio.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="349">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:13:46-03:00</t>
+    <t>2026-09-15T10:16:15-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -419,21 +419,21 @@
     <t>Specimen.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t xml:space="preserve">Extension
 </t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -443,30 +443,231 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Specimen.extension:motivoRechazo</t>
-  </si>
-  <si>
-    <t>motivoRechazo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {specimen-reject-reason}
+    <t>Specimen.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Motivo de rechazo de la muestra</t>
-  </si>
-  <si>
-    <t>Provides a code or text that specifies the reason a specimen is not usable for testing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
+    <t>External Identifier</t>
+  </si>
+  <si>
+    <t>Id for specimen.</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>SPM-2</t>
+  </si>
+  <si>
+    <t>Specimen.accessionIdentifier</t>
+  </si>
+  <si>
+    <t>Identifier assigned by the lab</t>
+  </si>
+  <si>
+    <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].act[classCode=ACSN, moodCode=EVN].id</t>
+  </si>
+  <si>
+    <t>SPM-30 (v2.7+)</t>
+  </si>
+  <si>
+    <t>Specimen.status</t>
+  </si>
+  <si>
+    <t>available | unavailable | unsatisfactory | entered-in-error</t>
+  </si>
+  <si>
+    <t>The availability of the specimen.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Codes providing the status/availability of a specimen.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-status|4.0.1</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>SPM-20</t>
+  </si>
+  <si>
+    <t>Specimen.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Specimen.extension:motivoRechazo.id</t>
-  </si>
-  <si>
-    <t>Specimen.extension.id</t>
+    <t>Kind of material that forms the specimen</t>
+  </si>
+  <si>
+    <t>The kind of material that forms the specimen.</t>
+  </si>
+  <si>
+    <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>The type of the specimen.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>SPM-4 and possibly SPM-5</t>
+  </si>
+  <si>
+    <t>Specimen.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/StructureDefinition/PacienteLaboratorio)
+</t>
+  </si>
+  <si>
+    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device</t>
+  </si>
+  <si>
+    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device.</t>
+  </si>
+  <si>
+    <t>Must know the subject context.</t>
+  </si>
+  <si>
+    <t>.scoper  or  .scoper.playsRole</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Specimen.receivedTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>The time when specimen was received for processing</t>
+  </si>
+  <si>
+    <t>Time when specimen was received for processing or testing.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].act[code=SPCREC, moodCode=EVN].effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>SPM-18</t>
+  </si>
+  <si>
+    <t>Specimen.parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Specimen from which this specimen originated</t>
+  </si>
+  <si>
+    <t>Reference to the parent (source) specimen which is used when the specimen was either derived from or a component of another specimen.</t>
+  </si>
+  <si>
+    <t>The parent specimen could be the source from which the current specimen is derived by some processing step (e.g. an aliquot or isolate or extracted nucleic acids from clinical samples) or one of many specimens that were combined to create a pooled sample.</t>
+  </si>
+  <si>
+    <t>.scoper (if parent) .player.scopesRole[classCode=SPEC].player (if child)</t>
+  </si>
+  <si>
+    <t>Specimen.request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/StructureDefinition/MinsalServiceRequestLab)
+</t>
+  </si>
+  <si>
+    <t>Why the specimen was collected</t>
+  </si>
+  <si>
+    <t>Details concerning a service request that required a specimen to be collected.</t>
+  </si>
+  <si>
+    <t>The request may be explicit or implied such with a ServiceRequest that requires a blood draw.</t>
+  </si>
+  <si>
+    <t>outboundRelationship[typeCode=FLFS].target</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>ORC? OBR-2/3?</t>
+  </si>
+  <si>
+    <t>Specimen.collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Collection details</t>
+  </si>
+  <si>
+    <t>Details concerning the specimen collection.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=SBJ].act[classCode=SPECCOLLECT, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>SPM-14</t>
+  </si>
+  <si>
+    <t>Specimen.collection.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -485,301 +686,13 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Specimen.extension:motivoRechazo.extension</t>
-  </si>
-  <si>
-    <t>Specimen.extension.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
+    <t>Specimen.collection.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Specimen.extension:motivoRechazo.url</t>
-  </si>
-  <si>
-    <t>Specimen.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/specimen-reject-reason</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Specimen.extension:motivoRechazo.value[x]</t>
-  </si>
-  <si>
-    <t>Specimen.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/ValueSet/motivo-rechazo-muestra-laboratorio</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Specimen.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Specimen.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>External Identifier</t>
-  </si>
-  <si>
-    <t>Id for specimen.</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>SPM-2</t>
-  </si>
-  <si>
-    <t>Specimen.accessionIdentifier</t>
-  </si>
-  <si>
-    <t>Identifier assigned by the lab</t>
-  </si>
-  <si>
-    <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].act[classCode=ACSN, moodCode=EVN].id</t>
-  </si>
-  <si>
-    <t>SPM-30 (v2.7+)</t>
-  </si>
-  <si>
-    <t>Specimen.status</t>
-  </si>
-  <si>
-    <t>available | unavailable | unsatisfactory | entered-in-error</t>
-  </si>
-  <si>
-    <t>The availability of the specimen.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Codes providing the status/availability of a specimen.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-status|4.0.1</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>SPM-20</t>
-  </si>
-  <si>
-    <t>Specimen.type</t>
-  </si>
-  <si>
-    <t>Kind of material that forms the specimen</t>
-  </si>
-  <si>
-    <t>The kind of material that forms the specimen.</t>
-  </si>
-  <si>
-    <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>The type of the specimen.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>SPM-4 and possibly SPM-5</t>
-  </si>
-  <si>
-    <t>Specimen.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/StructureDefinition/PacienteLaboratorio)
-</t>
-  </si>
-  <si>
-    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device</t>
-  </si>
-  <si>
-    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device.</t>
-  </si>
-  <si>
-    <t>Must know the subject context.</t>
-  </si>
-  <si>
-    <t>.scoper  or  .scoper.playsRole</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Specimen.receivedTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>The time when specimen was received for processing</t>
-  </si>
-  <si>
-    <t>Time when specimen was received for processing or testing.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].act[code=SPCREC, moodCode=EVN].effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>SPM-18</t>
-  </si>
-  <si>
-    <t>Specimen.parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Specimen from which this specimen originated</t>
-  </si>
-  <si>
-    <t>Reference to the parent (source) specimen which is used when the specimen was either derived from or a component of another specimen.</t>
-  </si>
-  <si>
-    <t>The parent specimen could be the source from which the current specimen is derived by some processing step (e.g. an aliquot or isolate or extracted nucleic acids from clinical samples) or one of many specimens that were combined to create a pooled sample.</t>
-  </si>
-  <si>
-    <t>.scoper (if parent) .player.scopesRole[classCode=SPEC].player (if child)</t>
-  </si>
-  <si>
-    <t>Specimen.request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interoperabilidad.minsal.cl/fhir/ig/laboratorio/StructureDefinition/MinsalServiceRequestLab)
-</t>
-  </si>
-  <si>
-    <t>Why the specimen was collected</t>
-  </si>
-  <si>
-    <t>Details concerning a service request that required a specimen to be collected.</t>
-  </si>
-  <si>
-    <t>The request may be explicit or implied such with a ServiceRequest that requires a blood draw.</t>
-  </si>
-  <si>
-    <t>outboundRelationship[typeCode=FLFS].target</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ORC? OBR-2/3?</t>
-  </si>
-  <si>
-    <t>Specimen.collection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Collection details</t>
-  </si>
-  <si>
-    <t>Details concerning the specimen collection.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=SBJ].act[classCode=SPECCOLLECT, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>SPM-14</t>
-  </si>
-  <si>
-    <t>Specimen.collection.id</t>
-  </si>
-  <si>
-    <t>Specimen.collection.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Specimen.collection.modifierExtension</t>
@@ -937,6 +850,9 @@
   </si>
   <si>
     <t>Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Codes describing the fasting status of the patient.</t>
@@ -1496,12 +1412,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM54"/>
+  <dimension ref="A1:AM49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="36.48828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="31.54296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="31.54296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
@@ -1524,10 +1440,10 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="48.234375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="79.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.25" customWidth="true" bestFit="true" hidden="true"/>
@@ -2440,7 +2356,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2459,15 +2375,17 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>76</v>
@@ -2504,14 +2422,16 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>135</v>
@@ -2529,7 +2449,7 @@
         <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>76</v>
@@ -2538,46 +2458,48 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I10" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="J10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>76</v>
       </c>
@@ -2625,7 +2547,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2634,13 +2556,13 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>76</v>
+        <v>128</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>76</v>
@@ -2649,12 +2571,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2665,25 +2587,25 @@
         <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2734,36 +2656,36 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>76</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2774,7 +2696,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2783,16 +2705,16 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2831,48 +2753,48 @@
         <v>76</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="AC12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AD12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AF12" t="s" s="2">
+      <c r="AL12" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AG12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>76</v>
-      </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2880,31 +2802,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2912,31 +2834,31 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="S13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="Z13" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -2954,10 +2876,10 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>85</v>
@@ -2966,24 +2888,24 @@
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>76</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2997,24 +2919,26 @@
         <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -3039,11 +2963,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -3061,7 +2987,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3076,56 +3002,54 @@
         <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>76</v>
+        <v>174</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="J15" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3180,30 +3104,30 @@
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3214,10 +3138,10 @@
         <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>76</v>
@@ -3226,13 +3150,13 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3283,13 +3207,13 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>76</v>
@@ -3298,21 +3222,21 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3323,7 +3247,7 @@
         <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
@@ -3332,18 +3256,20 @@
         <v>76</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -3392,13 +3318,13 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
@@ -3407,21 +3333,21 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>187</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3432,28 +3358,28 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>196</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3479,13 +3405,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3503,13 +3429,13 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
@@ -3518,21 +3444,21 @@
         <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3540,7 +3466,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>85</v>
@@ -3552,20 +3478,18 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3590,31 +3514,31 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="Y19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3629,21 +3553,21 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>206</v>
+        <v>76</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3651,33 +3575,31 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
       </c>
@@ -3725,7 +3647,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3737,13 +3659,13 @@
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>76</v>
@@ -3758,14 +3680,14 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3774,18 +3696,20 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N21" s="2"/>
+      <c r="N21" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
@@ -3834,40 +3758,40 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3880,24 +3804,26 @@
         <v>76</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
       </c>
@@ -3957,10 +3883,10 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>76</v>
@@ -3971,10 +3897,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3985,7 +3911,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>86</v>
@@ -3994,20 +3920,18 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -4056,13 +3980,13 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
@@ -4071,21 +3995,21 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4105,16 +4029,16 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4165,7 +4089,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4180,21 +4104,21 @@
         <v>97</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4214,16 +4138,16 @@
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>146</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4274,7 +4198,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>148</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4286,13 +4210,13 @@
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>76</v>
+        <v>235</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4300,21 +4224,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4326,17 +4250,15 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>173</v>
-      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4385,59 +4307,59 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>153</v>
+        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>76</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>248</v>
@@ -4445,12 +4367,8 @@
       <c r="M27" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>174</v>
-      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
       </c>
@@ -4474,13 +4392,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>76</v>
+        <v>250</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4498,36 +4416,36 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>128</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>76</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4547,18 +4465,20 @@
         <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>252</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4583,13 +4503,13 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>76</v>
+        <v>258</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>76</v>
@@ -4607,7 +4527,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4622,21 +4542,21 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>256</v>
+        <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4650,7 +4570,7 @@
         <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>76</v>
@@ -4659,16 +4579,20 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
@@ -4692,13 +4616,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>76</v>
+        <v>269</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4716,7 +4640,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4731,21 +4655,21 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4756,7 +4680,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -4765,16 +4689,16 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>266</v>
+        <v>204</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4825,13 +4749,13 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
@@ -4840,10 +4764,10 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>76</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>76</v>
@@ -4851,10 +4775,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4877,13 +4801,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>271</v>
+        <v>211</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4934,7 +4858,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4946,38 +4870,38 @@
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>274</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>76</v>
@@ -4986,15 +4910,17 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>132</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5019,94 +4945,96 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="J33" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>220</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5130,13 +5058,13 @@
         <v>76</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>286</v>
+        <v>76</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>287</v>
+        <v>76</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>76</v>
@@ -5154,36 +5082,36 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>288</v>
+        <v>128</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>289</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5203,23 +5131,19 @@
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>291</v>
+        <v>210</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
@@ -5243,13 +5167,13 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>296</v>
+        <v>76</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>76</v>
@@ -5267,7 +5191,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5282,21 +5206,21 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>76</v>
+        <v>282</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>298</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5307,7 +5231,7 @@
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5319,13 +5243,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>237</v>
+        <v>165</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5352,13 +5276,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>76</v>
+        <v>286</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5376,13 +5300,13 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
@@ -5391,7 +5315,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>302</v>
+        <v>172</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>76</v>
@@ -5402,10 +5326,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5416,7 +5340,7 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5428,13 +5352,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>145</v>
+        <v>289</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>146</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>147</v>
+        <v>291</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5485,47 +5409,47 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>149</v>
+        <v>292</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>76</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>76</v>
@@ -5537,17 +5461,15 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -5596,22 +5518,22 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>153</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>76</v>
@@ -5620,16 +5542,16 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5639,29 +5561,25 @@
         <v>78</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>130</v>
+        <v>204</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>76</v>
       </c>
@@ -5709,7 +5627,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5721,10 +5639,10 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>76</v>
@@ -5735,10 +5653,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5761,13 +5679,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>211</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>212</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5818,7 +5736,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>306</v>
+        <v>213</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5830,10 +5748,10 @@
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>309</v>
+        <v>214</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>76</v>
@@ -5844,21 +5762,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -5870,15 +5788,17 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>311</v>
+        <v>132</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>76</v>
@@ -5903,13 +5823,13 @@
         <v>76</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>313</v>
+        <v>76</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>314</v>
+        <v>76</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>76</v>
@@ -5927,22 +5847,22 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>217</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>76</v>
@@ -5953,14 +5873,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5973,22 +5893,26 @@
         <v>76</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>316</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>317</v>
+        <v>220</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
@@ -6036,7 +5960,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6048,24 +5972,24 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>319</v>
+        <v>128</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>320</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6076,7 +6000,7 @@
         <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>76</v>
@@ -6085,16 +6009,16 @@
         <v>76</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>259</v>
+        <v>143</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6145,13 +6069,13 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>76</v>
@@ -6160,21 +6084,21 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>262</v>
+        <v>146</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>76</v>
+        <v>307</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6185,10 +6109,10 @@
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>76</v>
@@ -6197,13 +6121,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6254,13 +6178,13 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
@@ -6269,7 +6193,7 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>76</v>
@@ -6278,12 +6202,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6297,7 +6221,7 @@
         <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>76</v>
@@ -6306,13 +6230,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>146</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>147</v>
+        <v>314</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6339,13 +6263,13 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>76</v>
+        <v>315</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6363,7 +6287,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>148</v>
+        <v>312</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6375,35 +6299,35 @@
         <v>76</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>76</v>
+        <v>317</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>170</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>76</v>
@@ -6415,17 +6339,15 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>244</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6474,72 +6396,68 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>153</v>
+        <v>318</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>149</v>
+        <v>321</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>76</v>
+        <v>322</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>130</v>
+        <v>242</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>248</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>76</v>
       </c>
@@ -6587,36 +6505,36 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>128</v>
+        <v>326</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>76</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6627,7 +6545,7 @@
         <v>77</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6636,16 +6554,16 @@
         <v>76</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>177</v>
+        <v>329</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6672,13 +6590,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>76</v>
+        <v>333</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6696,13 +6614,13 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
@@ -6711,21 +6629,21 @@
         <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>180</v>
+        <v>334</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6736,7 +6654,7 @@
         <v>77</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -6745,19 +6663,23 @@
         <v>76</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
       </c>
@@ -6781,13 +6703,13 @@
         <v>76</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>76</v>
+        <v>268</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>76</v>
@@ -6805,13 +6727,13 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>76</v>
@@ -6820,21 +6742,21 @@
         <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>338</v>
+        <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>76</v>
+        <v>343</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6845,10 +6767,10 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>76</v>
@@ -6857,13 +6779,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>163</v>
+        <v>345</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>50</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6890,13 +6812,13 @@
         <v>76</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>342</v>
+        <v>76</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>343</v>
+        <v>76</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>76</v>
@@ -6914,13 +6836,13 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>76</v>
@@ -6929,566 +6851,17 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>205</v>
+        <v>347</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK50" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>375</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM54">
+  <autoFilter ref="A1:AM49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7498,7 +6871,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fhir/ig/laboratorio/v0.1.0/StructureDefinition-MinsalEspecimenLaboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/StructureDefinition-MinsalEspecimenLaboratorio.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T10:16:15-03:00</t>
+    <t>2026-09-21T17:12:23-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/laboratorio/v0.1.0/StructureDefinition-MinsalEspecimenLaboratorio.xlsx
+++ b/fhir/ig/laboratorio/v0.1.0/StructureDefinition-MinsalEspecimenLaboratorio.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T17:12:23-03:00</t>
+    <t>2026-09-22T09:29:02-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Perfil para representar la muestra biológica asociada a una solicitud de laboratorio, cuando el sistema de origen informa esta información en el mensaje HL7 v2 (por ejemplo, en el segmento SPM de ORM^O01/ORU^R01).</t>
+    <t>Perfil para representar la muestra biológica asociada a una solicitud de laboratorio, cuando el sistema de origen informa esta información en el mensaje HL7 v2 (grupo SPM/SAC de OML^O21, mensaje objetivo para laboratorio, o en ORU^R01 al momento del resultado; ORM^O01 no incluye SPM/SAC en el estándar base, ver [Mapeo HL7 v2 a FHIR](mapeo-v2-fhir.html)).</t>
   </si>
   <si>
     <t>Purpose</t>
